--- a/EXP/模型数据统计.xlsx
+++ b/EXP/模型数据统计.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\Code\Python\FaultSeg3D_pytorch-main\EXP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFA6487D-A0D3-42FB-92B0-E2D94BD5D15B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E94FAFD-4A4F-4B71-9F8C-662E461A6F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -188,17 +188,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="3.2185714233406847E-2"/>
-          <c:y val="8.3746649916741606E-2"/>
-          <c:w val="0.94376297681643917"/>
-          <c:h val="0.81722887463859994"/>
-        </c:manualLayout>
-      </c:layout>
+      <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -207,11 +197,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'400_50_UNet_'!$D$1</c:f>
+              <c:f>'400_50_UNet_'!$F$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>train_dice</c:v>
+                  <c:v>val_iou</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -230,159 +220,159 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>'400_50_UNet_'!$D$2:$D$51</c:f>
+              <c:f>'400_50_UNet_'!$F$2:$F$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
                 <c:pt idx="0">
-                  <c:v>0.44740999999999997</c:v>
+                  <c:v>0.37801000000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.53576999999999997</c:v>
+                  <c:v>0.46594000000000002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.59199000000000002</c:v>
+                  <c:v>0.51688999999999996</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.63961999999999997</c:v>
+                  <c:v>0.58126999999999995</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.68464999999999998</c:v>
+                  <c:v>0.61623000000000006</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.71945000000000003</c:v>
+                  <c:v>0.62734999999999996</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.74348999999999998</c:v>
+                  <c:v>0.67056000000000004</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.76370000000000005</c:v>
+                  <c:v>0.69733999999999996</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.77698</c:v>
+                  <c:v>0.68589</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.78757999999999995</c:v>
+                  <c:v>0.70501000000000003</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.79329000000000005</c:v>
+                  <c:v>0.70228999999999997</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.80259000000000003</c:v>
+                  <c:v>0.72990999999999995</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.80879999999999996</c:v>
+                  <c:v>0.71172999999999997</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.81357000000000002</c:v>
+                  <c:v>0.70033999999999996</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.81857999999999997</c:v>
+                  <c:v>0.73072999999999999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.82308000000000003</c:v>
+                  <c:v>0.72770000000000001</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.82493000000000005</c:v>
+                  <c:v>0.72562000000000004</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.82881000000000005</c:v>
+                  <c:v>0.72713000000000005</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.83318000000000003</c:v>
+                  <c:v>0.75958000000000003</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.83528999999999998</c:v>
+                  <c:v>0.74424000000000001</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.83884000000000003</c:v>
+                  <c:v>0.74002999999999997</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.83828000000000003</c:v>
+                  <c:v>0.73251999999999995</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.84209999999999996</c:v>
+                  <c:v>0.74950000000000006</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.84521999999999997</c:v>
+                  <c:v>0.76290999999999998</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.84584999999999999</c:v>
+                  <c:v>0.74209000000000003</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.84784999999999999</c:v>
+                  <c:v>0.75580999999999998</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.84945999999999999</c:v>
+                  <c:v>0.75378999999999996</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.85160999999999998</c:v>
+                  <c:v>0.76856000000000002</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.85148000000000001</c:v>
+                  <c:v>0.74800999999999995</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.84967999999999999</c:v>
+                  <c:v>0.76092000000000004</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.85572999999999999</c:v>
+                  <c:v>0.77200999999999997</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.85270999999999997</c:v>
+                  <c:v>0.76273000000000002</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.86094000000000004</c:v>
+                  <c:v>0.77688000000000001</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.86211000000000004</c:v>
+                  <c:v>0.77222999999999997</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.86675000000000002</c:v>
+                  <c:v>0.76778000000000002</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.86438999999999999</c:v>
+                  <c:v>0.75094000000000005</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.85907999999999995</c:v>
+                  <c:v>0.77639999999999998</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.86639999999999995</c:v>
+                  <c:v>0.76649999999999996</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.86158000000000001</c:v>
+                  <c:v>0.77629999999999999</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.86980999999999997</c:v>
+                  <c:v>0.77927999999999997</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.87087999999999999</c:v>
+                  <c:v>0.78242999999999996</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.87131999999999998</c:v>
+                  <c:v>0.78195000000000003</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.86729000000000001</c:v>
+                  <c:v>0.77061999999999997</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.87192999999999998</c:v>
+                  <c:v>0.77776999999999996</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.86365000000000003</c:v>
+                  <c:v>0.77202999999999999</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.87314000000000003</c:v>
+                  <c:v>0.78922000000000003</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.87222999999999995</c:v>
+                  <c:v>0.78519000000000005</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.87851000000000001</c:v>
+                  <c:v>0.76897000000000004</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.87407999999999997</c:v>
+                  <c:v>0.77461999999999998</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.87487000000000004</c:v>
+                  <c:v>0.78327000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -390,7 +380,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8696-487C-AACB-4A6CAF79D718}"/>
+              <c16:uniqueId val="{00000000-CF95-43DA-84D8-38E5AB29C747}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -399,11 +389,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'400_50_UNet_'!$L$1</c:f>
+              <c:f>'400_50_UNet_'!$N$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>train_dice</c:v>
+                  <c:v>val_iou</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -422,159 +412,159 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>'400_50_UNet_'!$L$2:$L$51</c:f>
+              <c:f>'400_50_UNet_'!$N$2:$N$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
                 <c:pt idx="0">
-                  <c:v>0.54544999999999999</c:v>
+                  <c:v>0.49035000000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.64746999999999999</c:v>
+                  <c:v>0.58531</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.6875</c:v>
+                  <c:v>0.58787</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.71394000000000002</c:v>
+                  <c:v>0.58672000000000002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.73418000000000005</c:v>
+                  <c:v>0.62390000000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.75131999999999999</c:v>
+                  <c:v>0.66366999999999998</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.76298999999999995</c:v>
+                  <c:v>0.66378999999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.77412999999999998</c:v>
+                  <c:v>0.66266000000000003</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.78508999999999995</c:v>
+                  <c:v>0.69415000000000004</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.79417000000000004</c:v>
+                  <c:v>0.70389000000000002</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.79827999999999999</c:v>
+                  <c:v>0.69410000000000005</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.80676999999999999</c:v>
+                  <c:v>0.70238999999999996</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.80859000000000003</c:v>
+                  <c:v>0.72716999999999998</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.81579999999999997</c:v>
+                  <c:v>0.72499000000000002</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.81998000000000004</c:v>
+                  <c:v>0.74372000000000005</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.82723999999999998</c:v>
+                  <c:v>0.73531999999999997</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.82796999999999998</c:v>
+                  <c:v>0.71997999999999995</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.82733000000000001</c:v>
+                  <c:v>0.75651000000000002</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.83581000000000005</c:v>
+                  <c:v>0.74275000000000002</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.83843999999999996</c:v>
+                  <c:v>0.74472000000000005</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.84111000000000002</c:v>
+                  <c:v>0.73502000000000001</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.84287000000000001</c:v>
+                  <c:v>0.68932000000000004</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.84807999999999995</c:v>
+                  <c:v>0.75799000000000005</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.84491000000000005</c:v>
+                  <c:v>0.75031000000000003</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.85009999999999997</c:v>
+                  <c:v>0.76039000000000001</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.85245000000000004</c:v>
+                  <c:v>0.74924000000000002</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.85429999999999995</c:v>
+                  <c:v>0.76819999999999999</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.85590999999999995</c:v>
+                  <c:v>0.75668999999999997</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.85384000000000004</c:v>
+                  <c:v>0.73062000000000005</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.85348000000000002</c:v>
+                  <c:v>0.74753999999999998</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.86026999999999998</c:v>
+                  <c:v>0.76444000000000001</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.86502000000000001</c:v>
+                  <c:v>0.76314000000000004</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.86572000000000005</c:v>
+                  <c:v>0.76576999999999995</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.86765000000000003</c:v>
+                  <c:v>0.76134000000000002</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.86795</c:v>
+                  <c:v>0.77702000000000004</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.86792000000000002</c:v>
+                  <c:v>0.76554999999999995</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.86772000000000005</c:v>
+                  <c:v>0.78378000000000003</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.86892000000000003</c:v>
+                  <c:v>0.78583999999999998</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.87165999999999999</c:v>
+                  <c:v>0.77986</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.87455000000000005</c:v>
+                  <c:v>0.78695000000000004</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.87599000000000005</c:v>
+                  <c:v>0.78969</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.87822999999999996</c:v>
+                  <c:v>0.78893000000000002</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.87714999999999999</c:v>
+                  <c:v>0.79427999999999999</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.87887000000000004</c:v>
+                  <c:v>0.77502000000000004</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.87675999999999998</c:v>
+                  <c:v>0.78554999999999997</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.87826000000000004</c:v>
+                  <c:v>0.80276999999999998</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.88258999999999999</c:v>
+                  <c:v>0.79029000000000005</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.88292000000000004</c:v>
+                  <c:v>0.79481999999999997</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.88136000000000003</c:v>
+                  <c:v>0.79242999999999997</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.87992999999999999</c:v>
+                  <c:v>0.79285000000000005</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -582,7 +572,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-8696-487C-AACB-4A6CAF79D718}"/>
+              <c16:uniqueId val="{00000001-CF95-43DA-84D8-38E5AB29C747}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -591,11 +581,11 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'400_50_UNet_'!$T$1</c:f>
+              <c:f>'400_50_UNet_'!$V$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>train_dice</c:v>
+                  <c:v>val_iou</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -614,159 +604,159 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>'400_50_UNet_'!$T$2:$T$51</c:f>
+              <c:f>'400_50_UNet_'!$V$2:$V$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
                 <c:pt idx="0">
-                  <c:v>0.59138999999999997</c:v>
+                  <c:v>0.51600000000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.66981000000000002</c:v>
+                  <c:v>0.54874000000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.70657999999999999</c:v>
+                  <c:v>0.64709000000000005</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.73407999999999995</c:v>
+                  <c:v>0.64332</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.75470000000000004</c:v>
+                  <c:v>0.6704</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.77009000000000005</c:v>
+                  <c:v>0.70133000000000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.78212000000000004</c:v>
+                  <c:v>0.69152000000000002</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.79249000000000003</c:v>
+                  <c:v>0.69962999999999997</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.79925999999999997</c:v>
+                  <c:v>0.71782000000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.80817000000000005</c:v>
+                  <c:v>0.71813000000000005</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.81272999999999995</c:v>
+                  <c:v>0.74248000000000003</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.82186999999999999</c:v>
+                  <c:v>0.72897999999999996</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.82725000000000004</c:v>
+                  <c:v>0.73506000000000005</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.83067000000000002</c:v>
+                  <c:v>0.7298</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.83328000000000002</c:v>
+                  <c:v>0.72906000000000004</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.83908000000000005</c:v>
+                  <c:v>0.73709000000000002</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.84236999999999995</c:v>
+                  <c:v>0.75507000000000002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.84487999999999996</c:v>
+                  <c:v>0.75366999999999995</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.84801000000000004</c:v>
+                  <c:v>0.75899000000000005</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.85096000000000005</c:v>
+                  <c:v>0.77712999999999999</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.85185</c:v>
+                  <c:v>0.7702</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.85416999999999998</c:v>
+                  <c:v>0.78530999999999995</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.85680000000000001</c:v>
+                  <c:v>0.77778000000000003</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.86146999999999996</c:v>
+                  <c:v>0.78105000000000002</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.86014999999999997</c:v>
+                  <c:v>0.77527999999999997</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.85985</c:v>
+                  <c:v>0.78386</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.86087000000000002</c:v>
+                  <c:v>0.76775000000000004</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.86612</c:v>
+                  <c:v>0.77566999999999997</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.86909000000000003</c:v>
+                  <c:v>0.77788000000000002</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.87107000000000001</c:v>
+                  <c:v>0.77939000000000003</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.86924999999999997</c:v>
+                  <c:v>0.77754000000000001</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.87263999999999997</c:v>
+                  <c:v>0.79039000000000004</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.87436999999999998</c:v>
+                  <c:v>0.79386999999999996</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.87595000000000001</c:v>
+                  <c:v>0.80610999999999999</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.87607000000000002</c:v>
+                  <c:v>0.78456000000000004</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.87656000000000001</c:v>
+                  <c:v>0.79586999999999997</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.88004000000000004</c:v>
+                  <c:v>0.79359000000000002</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.87656999999999996</c:v>
+                  <c:v>0.79661999999999999</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.88175000000000003</c:v>
+                  <c:v>0.79576000000000002</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.87951999999999997</c:v>
+                  <c:v>0.80189999999999995</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.88185999999999998</c:v>
+                  <c:v>0.79539000000000004</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.88243000000000005</c:v>
+                  <c:v>0.80230000000000001</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.87873999999999997</c:v>
+                  <c:v>0.80876999999999999</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.88324999999999998</c:v>
+                  <c:v>0.80493999999999999</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.88534999999999997</c:v>
+                  <c:v>0.78705000000000003</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.88449999999999995</c:v>
+                  <c:v>0.81362999999999996</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.88478000000000001</c:v>
+                  <c:v>0.81277999999999995</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.88961000000000001</c:v>
+                  <c:v>0.80881999999999998</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.88688999999999996</c:v>
+                  <c:v>0.79981999999999998</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.88846999999999998</c:v>
+                  <c:v>0.80064999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -774,7 +764,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-8696-487C-AACB-4A6CAF79D718}"/>
+              <c16:uniqueId val="{00000002-CF95-43DA-84D8-38E5AB29C747}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -783,11 +773,11 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>'400_50_UNet_'!$AB$1</c:f>
+              <c:f>'400_50_UNet_'!$AD$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>train_dice</c:v>
+                  <c:v>val_iou</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -806,159 +796,159 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>'400_50_UNet_'!$AB$2:$AB$51</c:f>
+              <c:f>'400_50_UNet_'!$AD$2:$AD$51</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
                 <c:pt idx="0">
-                  <c:v>0.42693999999999999</c:v>
+                  <c:v>0.33300999999999997</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.53893999999999997</c:v>
+                  <c:v>0.60297000000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.69818000000000002</c:v>
+                  <c:v>0.63239000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.73851999999999995</c:v>
+                  <c:v>0.62414999999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.76141000000000003</c:v>
+                  <c:v>0.63441999999999998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.77334999999999998</c:v>
+                  <c:v>0.69916</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.78495999999999999</c:v>
+                  <c:v>0.69477</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.79437999999999998</c:v>
+                  <c:v>0.70957999999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.79823</c:v>
+                  <c:v>0.70147000000000004</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.80396000000000001</c:v>
+                  <c:v>0.68906999999999996</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.80642999999999998</c:v>
+                  <c:v>0.72045000000000003</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.80967999999999996</c:v>
+                  <c:v>0.72521000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.81337000000000004</c:v>
+                  <c:v>0.72450000000000003</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.82006000000000001</c:v>
+                  <c:v>0.72319</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.82064999999999999</c:v>
+                  <c:v>0.70881000000000005</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.82401999999999997</c:v>
+                  <c:v>0.74850000000000005</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.82962000000000002</c:v>
+                  <c:v>0.73255999999999999</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.83081000000000005</c:v>
+                  <c:v>0.73701000000000005</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.83403000000000005</c:v>
+                  <c:v>0.74412999999999996</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.83460000000000001</c:v>
+                  <c:v>0.73992999999999998</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.83260999999999996</c:v>
+                  <c:v>0.73924000000000001</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.83575999999999995</c:v>
+                  <c:v>0.74283999999999994</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.84153999999999995</c:v>
+                  <c:v>0.73512999999999995</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.84604999999999997</c:v>
+                  <c:v>0.76124999999999998</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.84857000000000005</c:v>
+                  <c:v>0.75163999999999997</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.84743999999999997</c:v>
+                  <c:v>0.74682999999999999</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.85131000000000001</c:v>
+                  <c:v>0.75685000000000002</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.85111999999999999</c:v>
+                  <c:v>0.76102999999999998</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.85372999999999999</c:v>
+                  <c:v>0.76936000000000004</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.85546999999999995</c:v>
+                  <c:v>0.77005000000000001</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.85738999999999999</c:v>
+                  <c:v>0.76078000000000001</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.85863</c:v>
+                  <c:v>0.74395</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.86204000000000003</c:v>
+                  <c:v>0.76895999999999998</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.86046999999999996</c:v>
+                  <c:v>0.76902999999999999</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.86358000000000001</c:v>
+                  <c:v>0.78532999999999997</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.86480999999999997</c:v>
+                  <c:v>0.76221000000000005</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.86475999999999997</c:v>
+                  <c:v>0.76881999999999995</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.86148000000000002</c:v>
+                  <c:v>0.76232</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.86724999999999997</c:v>
+                  <c:v>0.76090999999999998</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.87005999999999994</c:v>
+                  <c:v>0.78854999999999997</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.87077000000000004</c:v>
+                  <c:v>0.78251000000000004</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.86787000000000003</c:v>
+                  <c:v>0.76737</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.87063999999999997</c:v>
+                  <c:v>0.78851000000000004</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.86958000000000002</c:v>
+                  <c:v>0.77375000000000005</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.87226000000000004</c:v>
+                  <c:v>0.78785000000000005</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.87392000000000003</c:v>
+                  <c:v>0.77695000000000003</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.87607999999999997</c:v>
+                  <c:v>0.78520999999999996</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.87527999999999995</c:v>
+                  <c:v>0.79071999999999998</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.87895000000000001</c:v>
+                  <c:v>0.79271000000000003</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.88046000000000002</c:v>
+                  <c:v>0.78591999999999995</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -966,7 +956,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-8696-487C-AACB-4A6CAF79D718}"/>
+              <c16:uniqueId val="{00000003-CF95-43DA-84D8-38E5AB29C747}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -979,16 +969,17 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="850612639"/>
-        <c:axId val="1863761695"/>
+        <c:axId val="1795422815"/>
+        <c:axId val="1801298975"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="850612639"/>
+        <c:axId val="1795422815"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1025,7 +1016,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1863761695"/>
+        <c:crossAx val="1801298975"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1033,10 +1024,10 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1863761695"/>
+        <c:axId val="1801298975"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:min val="0.4"/>
+          <c:min val="0.5"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1085,7 +1076,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="850612639"/>
+        <c:crossAx val="1795422815"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1129,14 +1120,7 @@
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="zero"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
+    <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
@@ -1732,23 +1716,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>83128</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>76199</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>310340</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>73426</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>124692</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>41563</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>254923</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>116377</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="图表 4">
+        <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EB8BC02-E674-9721-87DF-433DA9F68994}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2C73E25-B9E7-BE03-1825-7B89F61BAEB3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2035,11 +2019,18 @@
   <dimension ref="A1:AE51"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="7" width="8.77734375" customWidth="1"/>
+    <col min="1" max="3" width="8.77734375" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="8.77734375" customWidth="1"/>
+    <col min="6" max="6" width="16.21875" customWidth="1"/>
+    <col min="7" max="7" width="8.77734375" customWidth="1"/>
     <col min="8" max="8" width="5.109375" customWidth="1"/>
     <col min="9" max="15" width="8.77734375" customWidth="1"/>
     <col min="16" max="16" width="4.77734375" customWidth="1"/>
-    <col min="17" max="23" width="8.77734375" customWidth="1"/>
+    <col min="17" max="17" width="15" customWidth="1"/>
+    <col min="18" max="18" width="13.21875" customWidth="1"/>
+    <col min="19" max="19" width="11.5546875" customWidth="1"/>
+    <col min="20" max="23" width="8.77734375" customWidth="1"/>
     <col min="24" max="24" width="4.33203125" customWidth="1"/>
     <col min="25" max="31" width="8.77734375" customWidth="1"/>
   </cols>
